--- a/output/pdf_financials_xlsx/CISC.xlsx
+++ b/output/pdf_financials_xlsx/CISC.xlsx
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.057202</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.035418</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.025574</v>
       </c>
     </row>
     <row r="104">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.670941</v>
+        <v>0.613739</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.211295</v>
+        <v>1.175877</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>3.413828</v>
+        <v>3.439402</v>
       </c>
     </row>
     <row r="107">
@@ -2776,7 +2776,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.202481</v>
       </c>
@@ -3805,7 +3809,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.057202</v>
       </c>

--- a/output/pdf_financials_xlsx/CISC.xlsx
+++ b/output/pdf_financials_xlsx/CISC.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.515725</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.096502</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.951735</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.515725</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.096502</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.951735</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>7.81112</v>
+        <v>7.295395</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.729292</v>
+        <v>2.63279</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.662855</v>
+        <v>1.71112</v>
       </c>
     </row>
     <row r="49">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.001328</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.001328</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4419,7 +4419,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>-0.001328</v>
       </c>

--- a/output/pdf_financials_xlsx/CISC.xlsx
+++ b/output/pdf_financials_xlsx/CISC.xlsx
@@ -1066,7 +1066,7 @@
         <v>0.141774</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.073187</v>
       </c>
     </row>
     <row r="41">
@@ -1082,7 +1082,7 @@
         <v>0.141774</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.073187</v>
       </c>
     </row>
     <row r="42">
@@ -1194,7 +1194,7 @@
         <v>2.63279</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.71112</v>
+        <v>1.637933</v>
       </c>
     </row>
     <row r="49">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>5.855923</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>3.561008</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>5.559365</v>
       </c>
     </row>
     <row r="65">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.758072</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.566259</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.959687</v>
       </c>
     </row>
     <row r="68">
